--- a/donnees_test/reel_2026_10_errone.xlsx
+++ b/donnees_test/reel_2026_10_errone.xlsx
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>OUJDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
